--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0223.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0223.xlsx
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>&lt;color=#e2524c&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Bộ bài sẽ được tạo từ thiết lập có sẵn đã chọn và sẽ &lt;color=#e2524c&gt;overwrite&lt;/color&gt; lên bộ bài hiện tại của bạn. Tiếp tục chứ?</t>
+          <t>Bộ bài sẽ được tạo từ thiết lập có sẵn đã chọn và sẽ &lt;color=#e2524c&gt;ghi đè&lt;/color&gt; lên bộ bài hiện tại của bạn. Tiếp tục chứ?</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>&lt;color=#f09f4e&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>&lt;color=#f09f4e&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>&lt;color=#c7fe96&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>&lt;color=#ff758d&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
+          <t>&lt;color=#c79f49&gt;Giấc Mơ Phân Tầng&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
+          <t>&lt;color=#c79f49&gt;Giấc Mơ Nuốt Chửng&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>&lt;color=#c79f49&gt;Dream of Exchange&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
+          <t>&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>&lt;color=#c79f49&gt;Dream of Integration&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
+          <t>&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt; có khả năng xuất hiện Echo cao hơn.</t>
         </is>
       </c>
     </row>
@@ -14551,7 +14551,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Tất Cả Ra Trận! Vươn Tới Đỉnh Danh Vọng</t>
+          <t>Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>&lt;color=#ffc802&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 Cộng Hưởng Giả bất kỳ lên cấp 30.</t>
+          <t>Nâng cấp 3 Resonator bất kỳ lên cấp 30.</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Cấp 60.</t>
+          <t>Nâng cấp 1 Resonator lên Cấp 60.</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Flash&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, dịch chuyển Tổ Tacet này đến Khu Hậu Cảnh của đối phương.</t>
+          <t>&lt;color=#e4c69b&gt;Thần Tốc&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Giai Đoạn Chiến Đấu bắt đầu, dịch chuyển Tổ Tacet này đến Khu Hậu Cảnh của đối phương.</t>
         </is>
       </c>
     </row>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Cycle&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Tái cấu trúc Tacet Discord này sẽ cung cấp thêm {0} điểm Năng Lượng.</t>
+          <t>&lt;color=#e4c69b&gt;Cycle&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Tái cấu trúc Tacet Discord này sẽ cung cấp thêm {0} điểm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22676,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Mời Cộng Hưởng Giả đến suối nước nóng Thermes lần đầu</t>
+          <t>Mời Resonator đến suối nước nóng Thermes lần đầu</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thu thập tất cả Tiếng Vang trong "Tất Sả! Vươn Tới Đỉnh Vinh Quang".</t>
+          <t>Thu thập tất cả Echo trong "Tất Sả! Vươn Tới Đỉnh Vinh Quang".</t>
         </is>
       </c>
     </row>
@@ -22871,7 +22871,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Thu thập tất cả Chiến Thuật Cộng Hưởng Giả trong "Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng."</t>
+          <t>Thu thập tất cả Chiến Thuật Resonator trong "Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng."</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Kế Hoạch Quản Lý Tiếng Vọng từ Rover {0}: {1}</t>
+          <t>Kế Hoạch Quản Lý Tiếng Vọng từ Vận Mệnh Giả {0}: {1}</t>
         </is>
       </c>
     </row>
@@ -25926,7 +25926,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Sau {0} ngày, &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; và nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Sau {0} ngày, &lt;te href=851041&gt;&lt;color=#c79f49&gt;Xóa bỏ&lt;/color&gt;&lt;/te&gt; và nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Dreamland&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Có thể coi như một Echo thuộc bất kỳ độ hiếm nào khi thực hiện &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Có thể coi như một Echo thuộc bất kỳ độ hiếm nào khi thực hiện &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Vào đầu mỗi ngày, có {0}% cơ hội tạo ra 1 &lt;te href=851046&gt;&lt;color=#c79f49&gt;Fission Junrock&lt;/color&gt;&lt;/te&gt; trên ô trống.</t>
+          <t>Vào đầu mỗi ngày, có {0}% cơ hội tạo ra 1 &lt;te href=851046&gt;&lt;color=#c79f49&gt;Đá Phân Rã Junrock&lt;/color&gt;&lt;/te&gt; trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -26511,7 +26511,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Chi phí 3 Tiếng Vang không thể Điều Tần.</t>
+          <t>Chi phí 3 Echo không thể Điều Tần.</t>
         </is>
       </c>
     </row>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>&lt;te href=851014&gt;&lt;color=#c79f49&gt;Rooted&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851014&gt;&lt;color=#c79f49&gt;Bám Rễ&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>&lt;te href=851051&gt;&lt;color=#c79f49&gt;Adjacent&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851051&gt;&lt;color=#c79f49&gt;Liền Kề&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -27096,7 +27096,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -27161,7 +27161,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>&lt;te href=851052&gt;&lt;color=#c79f49&gt;Same Row&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851052&gt;&lt;color=#c79f49&gt;Cùng Hàng&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>&lt;te href=851053&gt;&lt;color=#c79f49&gt;Any Rarity&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851053&gt;&lt;color=#c79f49&gt;Bất Kỳ Độ Hiếm Nào&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30216,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Vào đầu mỗi ngày, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Vào đầu mỗi ngày, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Cảnh&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Vào đầu mỗi ngày, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của một Echo ngẫu nhiên sẽ tăng thêm {0}.</t>
+          <t>Vào đầu mỗi ngày, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của một Echo ngẫu nhiên sẽ tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -30541,7 +30541,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Sau 1 ngày, nhận được {0} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt;. Hiệu ứng này chỉ kích hoạt một lần duy nhất.</t>
+          <t>Sau 1 ngày, nhận được {0} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt;&lt;/te&gt;. Hiệu ứng này chỉ kích hoạt một lần duy nhất.</t>
         </is>
       </c>
     </row>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt; sau mỗi {0} ngày.</t>
+          <t>Nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt;&lt;/te&gt; sau mỗi {0} ngày.</t>
         </is>
       </c>
     </row>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Thu hồi một Echo sẽ nhận thêm {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Thu hồi một Echo sẽ nhận thêm {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Dreamland&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hủy bỏ Echo sẽ nhận thêm {0} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Hủy bỏ Echo sẽ nhận thêm {0} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -31061,7 +31061,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Mỗi khi &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devour&lt;/color&gt;&lt;/te&gt; xảy ra, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Mỗi khi &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; xảy ra, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảo&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tất cả Echo trên Khối Mộng Ảo: Gương Nước được coi là &lt;te href=851055&gt;&lt;color=#c79f49&gt;adjacent&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Tất cả Echo trên Khối Mộng Ảo: Gương Nước được coi là &lt;te href=851055&gt;&lt;color=#c79f49&gt;kề nhau&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Cho ra lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; khá ổn định.</t>
+          <t>Cho ra lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; khá ổn định.</t>
         </is>
       </c>
     </row>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Khi thực hiện hành động đầu tiên, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;. Hiệu ứng này chỉ kích hoạt một lần duy nhất.</t>
+          <t>Khi thực hiện hành động đầu tiên, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảo&lt;/color&gt;&lt;/te&gt;. Hiệu ứng này chỉ kích hoạt một lần duy nhất.</t>
         </is>
       </c>
     </row>
@@ -31841,7 +31841,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Cho sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; cực cao.</t>
+          <t>Cho sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; cực cao.</t>
         </is>
       </c>
     </row>
@@ -31906,7 +31906,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystal&lt;/color&gt;&lt;/te&gt; sau mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}.</t>
+          <t>Nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt;&lt;/te&gt; sau mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}.</t>
         </is>
       </c>
     </row>
@@ -32946,7 +32946,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>&lt;color=#fee7a1ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -33011,7 +33011,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>&lt;size=36&gt;&lt;color=#e4e4e4ff&gt;Level&lt;/color&gt;&lt;/size&gt; &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;</t>
+          <t>&lt;size=36&gt;&lt;color=#e4e4e4ff&gt;Cấp độ&lt;/color&gt;&lt;/size&gt; &lt;color=#fde7a1ff&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
